--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_project_subject_domain_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_project_subject_domain_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="进度信息汇总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ods_project_subject_domain_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,215 +413,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AG51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>分系统/分任务</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>节点任务及目标</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>计划开始日期</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>节点计划时间</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>节点计划周数</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>交付物</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>节点类型</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>责任科室</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>分管室领导</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>完成情况</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>协同部门</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>责任监管部门</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>延期预计完成时间</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>未完成原因及当前进展</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>风险等级</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>主要风险内容及措施</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>延期影响分析</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>实际开始日期</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>实际完成时间</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>实际完成周数</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>所领导</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>延期项目原计划时间</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>计划延误时间(已变更)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>计划延误时间(未变更)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>是否提交延期申请</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>项目主管</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新周数</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>填写人</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>亮点工作</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subsystem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>node_task</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>plan_start_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>plan_date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>plan_week</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>deliverable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>node_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dept</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dept_leader</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>completion_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>collab_dept</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>supervisor_dept</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>delay_expected_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>incomplete_reason</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>risk_level</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>risk_content</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>delay_impact</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>actual_start_date</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>actual_date</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>actual_week</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>institute_leader</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>original_plan_date</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>delay_days_changed</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>delay_days_unchanged</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>delay_applied</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>project_manager</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>last_update_time</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>last_update_week</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>filled_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>highlight</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -643,25 +596,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>项目总方案设计评审</t>
+          <t>综合统筹平台需求基线评审</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>总体方案设计报告</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -691,7 +646,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>控制室;结构室</t>
+          <t>控制室;动力室</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -699,18 +654,25 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>9</v>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -722,6 +684,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>否</t>
@@ -734,11 +699,13 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>9</v>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -747,42 +714,44 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>提前1天完成</t>
+          <t>综合统筹平台 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>控制分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>控制器硬件方案评审</t>
+          <t>综合统筹平台详细设计评审</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>17</v>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>控制器硬件方案</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -792,27 +761,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>陈工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>总体室</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>控制室;动力室</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -820,18 +789,41 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>跨专业接口澄清耗时</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>综合统筹平台接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>影响后续任务5天</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>17</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -843,9 +835,16 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -855,75 +854,85 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>陈工</t>
-        </is>
-      </c>
+          <t>王工</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>控制分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>控制软件初样验证</t>
+          <t>综合统筹平台关键件交付</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>28</v>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>软件验证报告</t>
+          <t>综合控制机机箱</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>刘工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>总体室</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>超期已完成未变更</t>
+          <t>正常待完成</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>控制室;动力室</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -931,11 +940,8 @@
           <t>质量部</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>评审意见修改耗时</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>中</t>
@@ -943,27 +949,13 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>软件bug修复</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>延期10天</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>29</v>
-      </c>
+          <t>综合统筹平台关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>李所</t>
@@ -974,12 +966,12 @@
           <t>年度计划</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>10</v>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -989,95 +981,128 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>29</v>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>刘工</t>
+          <t>王工</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>结构分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>机械结构件加工</t>
+          <t>综合统筹平台联调准备</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>结构件实物</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>一般节点</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>周工</t>
+          <t>王工</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>结构室</t>
+          <t>总体室</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>吴总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期未完成未变更</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>工艺室</t>
+          <t>控制室;动力室</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>关键件到货晚于计划</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>综合控制机机箱交付滞后</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>影响联调窗口排布</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>38</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1088,6 +1113,13 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>否</t>
@@ -1100,55 +1132,60 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>38</v>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>周工</t>
-        </is>
-      </c>
+          <t>王工</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>初样联试联调</t>
+          <t>综合统筹平台综合联试</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>51</v>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>联试联调报告</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1168,32 +1205,47 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>不正常待变更</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>控制室;结构室</t>
+          <t>控制室;动力室</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>质量部</t>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>综合统筹平台需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>51</v>
-      </c>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1204,9 +1256,12 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1216,50 +1271,55 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>51</v>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
           <t>王工</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>正样设计评审</t>
+          <t>飞控执行机构需求基线评审</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>11</v>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>正样设计报告</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1269,27 +1329,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>王工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>总体室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>张总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>按时完成</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>控制室;结构室</t>
+          <t>动力室;制导室</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1297,6 +1357,26 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1307,6 +1387,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>否</t>
@@ -1314,91 +1397,136 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>孙PM</t>
+          <t>陈PM</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>陈工</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>飞控执行机构 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>发动机点火控制总方案</t>
+          <t>飞控执行机构详细设计评审</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>控制总方案</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>里程碑</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成已变更</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>动力室;制导室</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>科技部</t>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>新增评审意见需要补充闭环</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>飞控执行机构设计闭环补充验证</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>影响后续任务7天</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>10</v>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1410,87 +1538,108 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>陈PM</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>10</v>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>赵工</t>
-        </is>
-      </c>
+          <t>陈工</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>控制器选型评审</t>
+          <t>飞控执行机构关键件交付</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>18</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>选型报告</t>
+          <t>飞控控制器样机</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>正常待完成</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>动力室;制导室</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1498,19 +1647,22 @@
           <t>质量部</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>19</v>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>飞控执行机构关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1521,9 +1673,9 @@
           <t>年度计划</t>
         </is>
       </c>
-      <c r="Z9" t="n">
-        <v>3</v>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
           <t>否</t>
@@ -1531,55 +1683,64 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>陈PM</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>19</v>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>试验台架搭建</t>
+          <t>飞控执行机构联调准备</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>33</v>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>试验台架</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1589,42 +1750,66 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>钱工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期未完成已变更</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>工艺室</t>
+          <t>动力室;制导室</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>接口边界调整后重新排产</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>飞控执行机构联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>影响后续综合联试安排</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>33</v>
-      </c>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1635,107 +1820,119 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>陈PM</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AE10" t="n">
-        <v>33</v>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>钱工</t>
-        </is>
-      </c>
+          <t>陈工</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>热试车</t>
+          <t>飞控执行机构综合联试</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>48</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>热试车报告</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>陈工</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>超期未完成已变更</t>
+          <t>不正常待变更</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>工艺室</t>
+          <t>动力室;制导室</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>质量部</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>试车异常排查</t>
+          <t>发现外部约束变化需发起设计更改</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1745,19 +1942,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>试车后出现异常振动，技术归零进行中</t>
+          <t>飞控执行机构需新增变更评审</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>影响后续节点15周</t>
+          <t>影响综合联试基线冻结</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1768,14 +1967,9 @@
           <t>年度计划</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>56</v>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
           <t>是</t>
@@ -1783,19 +1977,30 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>陈PM</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>赵工</t>
-        </is>
-      </c>
+          <t>陈工</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1805,25 +2010,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>总装</t>
+          <t>姿轨动力系统需求基线评审</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>16</v>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>总装实物</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,12 +2055,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>按时完成</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>工艺室</t>
+          <t>制导室;软件室</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1861,6 +2068,26 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>李所</t>
@@ -1871,6 +2098,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
           <t>否</t>
@@ -1879,90 +2109,135 @@
       <c r="AC12" t="inlineStr">
         <is>
           <t>赵PM</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>姿轨动力系统 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>制导方案设计评审</t>
+          <t>姿轨动力系统详细设计评审</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>9</v>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>制导设计方案</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>里程碑</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>动力室</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>控制室;结构室</t>
+          <t>制导室;软件室</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>科技部</t>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>跨专业接口澄清耗时</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>姿轨动力系统接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>影响后续任务7天</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>9</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1974,97 +2249,104 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>林PM</t>
+          <t>赵PM</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>9</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>林工</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>评审优秀</t>
-        </is>
-      </c>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>制导算法设计</t>
+          <t>姿轨动力系统关键件交付</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>17</v>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>算法设计文档</t>
+          <t>动力控制组件</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>动力室</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>正常待完成</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>制导室;软件室</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2072,19 +2354,22 @@
           <t>质量部</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>17</v>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>姿轨动力系统关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2095,6 +2380,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
           <t>否</t>
@@ -2102,55 +2390,64 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>林PM</t>
+          <t>赵PM</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
-        <v>17</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>制导仿真验证</t>
+          <t>姿轨动力系统联调准备</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>28</v>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仿真验证报告</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2160,27 +2457,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>赵工</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>动力室</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成未变更</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>制导室;软件室</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2188,6 +2485,38 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>关键件到货晚于计划</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>动力控制组件交付滞后</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>影响联调窗口排布</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2198,6 +2527,13 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>否</t>
@@ -2205,74 +2541,125 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>林PM</t>
-        </is>
-      </c>
+          <t>赵PM</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>制导初样硬件调试</t>
+          <t>姿轨动力系统综合联试</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>综合联试纪要</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>动力室</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>孙总</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>不正常待变更</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>制导室;软件室</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>姿轨动力系统需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>38</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>硬件调试报告</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>重要节点</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>黄工</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>制导室</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>马总</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>正常待完成</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>质量部</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2283,54 +2670,75 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>林PM</t>
-        </is>
-      </c>
+          <t>赵PM</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>赵工</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>制导初样联试</t>
+          <t>惯导制导系统需求基线评审</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>50</v>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>联试报告</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2350,17 +2758,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>按时完成</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>控制室;结构室</t>
+          <t>软件室;结构室</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>质量部</t>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2373,6 +2801,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
           <t>否</t>
@@ -2381,90 +2812,135 @@
       <c r="AC17" t="inlineStr">
         <is>
           <t>林PM</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>林工</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>惯导制导系统 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>遥测遥控总方案评审</t>
+          <t>惯导制导系统详细设计评审</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>遥测总方案</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>里程碑</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>电子室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>郑总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成已变更</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>软件室;结构室</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>科技部</t>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>新增评审意见需要补充闭环</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>惯导制导系统设计闭环补充验证</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>影响后续任务9天</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2476,92 +2952,108 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>徐PM</t>
+          <t>林PM</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>10</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>徐工</t>
-        </is>
-      </c>
+          <t>林工</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>遥测天线设计</t>
+          <t>惯导制导系统关键件交付</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>19</v>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>天线设计方案</t>
+          <t>制导计算机板卡</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>电子室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>郑总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>超期已完成已变更</t>
+          <t>正常待完成</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>结构室</t>
+          <t>软件室;结构室</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2569,34 +3061,22 @@
           <t>质量部</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>仿真参数迭代</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>延期5天</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>20</v>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>惯导制导系统关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2607,70 +3087,74 @@
           <t>年度计划</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>5</v>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>徐PM</t>
+          <t>林PM</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AE19" t="n">
-        <v>20</v>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>林工</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>遥测终端研制</t>
+          <t>惯导制导系统联调准备</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>32</v>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>终端样机</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2680,22 +3164,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>何工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>电子室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>郑总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成已变更</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>软件室;结构室</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2703,6 +3192,38 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>接口边界调整后重新排产</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>惯导制导系统联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>影响后续综合联试安排</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2713,86 +3234,143 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>徐PM</t>
-        </is>
-      </c>
+          <t>林PM</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>林工</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>软件分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>遥控协议软件</t>
+          <t>惯导制导系统综合联试</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>37</v>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>协议软件V1.0</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>郭工</t>
+          <t>林工</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>朱总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>不正常待变更</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>电子室</t>
+          <t>软件室;结构室</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>质量部</t>
-        </is>
-      </c>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>惯导制导系统需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>李所</t>
@@ -2803,84 +3381,125 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>徐PM</t>
-        </is>
-      </c>
+          <t>林PM</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>林工</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>遥测遥控联试</t>
+          <t>实时软件平台需求基线评审</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>51</v>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>联试报告</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>徐工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>电子室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>郑总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>按时完成</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>结构室;电源室</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>质量部</t>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2893,6 +3512,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
           <t>否</t>
@@ -2900,91 +3522,136 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>徐PM</t>
+          <t>沈PM</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>沈工</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>实时软件平台 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>电源系统总体设计</t>
+          <t>实时软件平台详细设计评审</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>11</v>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>电源总体方案</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>里程碑</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成未变更</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>结构室</t>
+          <t>结构室;电源室</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>科技部</t>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>跨专业接口澄清耗时</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>实时软件平台接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>影响后续任务6天</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>11</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2996,173 +3663,205 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>宋PM</t>
+          <t>沈PM</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AE23" t="n">
-        <v>11</v>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>宋工</t>
-        </is>
-      </c>
+          <t>沈工</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>蓄电池组研制</t>
+          <t>实时软件平台关键件交付</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>23</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>蓄电池组实物</t>
+          <t>实时软件构件包</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>正常待完成</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>工艺室</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>23</v>
+          <t>结构室;电源室</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>实时软件平台关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>李所</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>沈PM</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>宋PM</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>23</v>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>沈工</t>
+        </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>配电器研制</t>
+          <t>实时软件平台联调准备</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>34</v>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>配电器样机</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3172,22 +3871,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>韩工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成未变更</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>结构室;电源室</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3195,6 +3899,38 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>关键件到货晚于计划</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>实时软件构件包交付滞后</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>影响联调窗口排布</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>李所</t>
@@ -3205,6 +3941,13 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>否</t>
@@ -3212,74 +3955,125 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>宋PM</t>
-        </is>
-      </c>
+          <t>沈PM</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>沈工</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>电源系统集成测试</t>
+          <t>实时软件平台综合联试</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>46</v>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>集成测试报告</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>宋工</t>
+          <t>沈工</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>不正常待变更</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>结构室;电源室</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>质量部</t>
-        </is>
-      </c>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>实时软件平台需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>李所</t>
@@ -3290,21 +4084,40 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>宋PM</t>
-        </is>
-      </c>
+          <t>沈PM</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>沈工</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3314,25 +4127,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>主承力结构方案评审</t>
+          <t>复合结构组件需求基线评审</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>14</v>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>结构方案</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3342,7 +4157,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3362,7 +4177,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>总体室</t>
+          <t>电源室;电子室</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3370,18 +4185,25 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>14</v>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3393,6 +4215,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
           <t>否</t>
@@ -3400,27 +4225,34 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>邓PM</t>
+          <t>周PM</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AE27" t="n">
-        <v>14</v>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>复合结构组件 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3430,25 +4262,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>结构有限元仿真</t>
+          <t>复合结构组件详细设计评审</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>24</v>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>仿真报告</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3458,7 +4292,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3473,7 +4307,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>超期已完成已变更</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>电源室;电子室</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3481,57 +4320,94 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>新增评审意见需要补充闭环</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>复合结构组件设计闭环补充验证</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>影响后续任务7天</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>24</v>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>李所</t>
+          <t>年度计划</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>年度计划</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>周PM</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>邓PM</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>邓工</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>周工</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3541,35 +4417,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>结构件试制</t>
+          <t>复合结构组件关键件交付</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>39</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>结构件实物</t>
+          <t>主承力舱段结构件</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>一般节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>余工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3589,9 +4467,30 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>工艺室</t>
-        </is>
-      </c>
+          <t>电源室;电子室</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>复合结构组件关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>李所</t>
@@ -3602,6 +4501,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr">
         <is>
           <t>否</t>
@@ -3609,14 +4511,34 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>邓PM</t>
+          <t>周PM</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>周工</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3626,35 +4548,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>结构静力试验</t>
+          <t>复合结构组件联调准备</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>50</v>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>试验报告</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>邓工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3669,12 +4593,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成已变更</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>工艺室</t>
+          <t>电源室;电子室</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3682,6 +4606,38 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>接口边界调整后重新排产</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>复合结构组件联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>影响后续综合联试安排</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>李所</t>
@@ -3692,49 +4648,78 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>邓PM</t>
-        </is>
-      </c>
+          <t>周PM</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>周工</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>测控分系统</t>
+          <t>结构分系统</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>测控系统总方案</t>
+          <t>复合结构组件综合联试</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>13</v>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>测控总方案</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3744,27 +4729,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>周工</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>测控室</t>
+          <t>结构室</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>吴总</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>不正常待变更</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>电源室;电子室</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3772,19 +4757,34 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>复合结构组件需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>13</v>
-      </c>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>李所</t>
@@ -3795,126 +4795,126 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>田PM</t>
+          <t>周PM</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AE31" t="n">
-        <v>13</v>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>田工</t>
-        </is>
-      </c>
+          <t>周工</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>测控分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>测控主机研制</t>
+          <t>高可靠电源系统需求基线评审</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>25</v>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>主机样机</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>测控室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>超期已完成已变更</t>
+          <t>按时完成</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>电子室;测控室</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>质量部</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>元器件到货延迟</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>排查原因并更换备选元器件</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>延期7天</t>
-        </is>
-      </c>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>26</v>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3926,70 +4926,74 @@
           <t>年度计划</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AA32" t="n">
-        <v>7</v>
-      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>田PM</t>
+          <t>宋PM</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AE32" t="n">
-        <v>26</v>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>高可靠电源系统 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>测控分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>测控软件开发</t>
+          <t>高可靠电源系统详细设计评审</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>30</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>软件V1.0</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3999,22 +5003,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>姜工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>朱总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期已完成未变更</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>电子室;测控室</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4022,6 +5031,42 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>跨专业接口澄清耗时</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>高可靠电源系统接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>影响后续任务5天</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4032,69 +5077,94 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>田PM</t>
-        </is>
-      </c>
+          <t>宋PM</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>宋工</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>测控分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>测控地面站调试</t>
+          <t>高可靠电源系统关键件交付</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>41</v>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>调试报告</t>
+          <t>电源管理单元</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>重大节点</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>测控室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4102,11 +5172,32 @@
           <t>正常待完成</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>电子室;测控室</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>质量部</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>高可靠电源系统关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4117,6 +5208,9 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr">
         <is>
           <t>否</t>
@@ -4124,72 +5218,94 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>田PM</t>
+          <t>宋PM</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>宋工</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>测控全链路联试</t>
+          <t>高可靠电源系统联调准备</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>52</v>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>联试报告</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>重大节点</t>
+          <t>重要节点</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>田工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>测控室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>潘总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期未完成未变更</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>电子室;测控室</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4197,6 +5313,38 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>关键件到货晚于计划</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>电源管理单元交付滞后</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>影响联调窗口排布</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4207,6 +5355,13 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AB35" t="inlineStr">
         <is>
           <t>否</t>
@@ -4214,42 +5369,60 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>田PM</t>
-        </is>
-      </c>
+          <t>宋PM</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>宋工</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>综合试验大纲评审</t>
+          <t>高可靠电源系统综合联试</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>17</v>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>试验大纲</t>
+          <t>综合联试纪要</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4259,27 +5432,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>宋工</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>试验室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>曹总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>按时完成</t>
+          <t>不正常待变更</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>全所</t>
+          <t>电子室;测控室</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4287,19 +5460,34 @@
           <t>科技部</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>高可靠电源系统需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>17</v>
-      </c>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4310,82 +5498,90 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>柳PM</t>
+          <t>宋PM</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AE36" t="n">
-        <v>17</v>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>柳工</t>
-        </is>
-      </c>
+          <t>宋工</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>环境试验</t>
+          <t>电子载荷组件需求基线评审</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>29</v>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>环境试验报告</t>
+          <t>需求基线包</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>重要节点</t>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>徐工</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>试验室</t>
+          <t>电子室</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>曹总</t>
+          <t>郑总</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4395,93 +5591,112 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>质量管理科</t>
+          <t>测控室;试验室</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>质量部</t>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>29</v>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>李所</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>徐PM</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>柳PM</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>29</v>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>电子载荷组件 需求基线评审一次通过</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>电磁兼容试验</t>
+          <t>电子载荷组件详细设计评审</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>39</v>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EMC试验报告</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4491,22 +5706,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>徐工</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>试验室</t>
+          <t>电子室</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>曹总</t>
+          <t>郑总</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>正常待完成</t>
+          <t>超期已完成已变更</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>测控室;试验室</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4514,6 +5734,42 @@
           <t>质量部</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>新增评审意见需要补充闭环</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>电子载荷组件设计闭环补充验证</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>影响后续任务9天</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4524,49 +5780,78 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>柳PM</t>
-        </is>
-      </c>
+          <t>徐PM</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>可靠性试验</t>
+          <t>电子载荷组件关键件交付</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>50</v>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>可靠性报告</t>
+          <t>载荷处理模块</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4576,27 +5861,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>徐工</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>试验室</t>
+          <t>电子室</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>曹总</t>
+          <t>郑总</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>不正常待变更</t>
+          <t>正常待完成</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>全所</t>
+          <t>测控室;试验室</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4604,31 +5889,22 @@
           <t>质量部</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>发现局部可靠性不达标需变更设计</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>部分模块可靠性不满足要求</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>后续设计需整改</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
+          <t>电子载荷组件关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>李所</t>
@@ -4639,111 +5915,1743 @@
           <t>年度计划</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>柳PM</t>
+          <t>徐PM</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>柳工</t>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>出所鉴定试验</t>
+          <t>电子载荷组件联调准备</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>5</v>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>鉴定报告</t>
+          <t>联调准备报告</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>重要节点</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>电子室</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>郑总</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>超期未完成已变更</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>测控室;试验室</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>接口边界调整后重新排产</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>电子载荷组件联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>影响后续综合联试安排</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>徐PM</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>XM-2026-C08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>电子分系统</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>电子载荷组件综合联试</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>综合联试纪要</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>电子室</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>郑总</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>不正常待变更</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>测控室;试验室</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>电子载荷组件需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>徐PM</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>2027-04-03</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>徐工</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>测控链路系统需求基线评审</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>需求基线包</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>按时完成</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>试验室;总体室</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>测控链路系统 需求基线评审一次通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>测控链路系统详细设计评审</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>详细设计报告</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>重要节点</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>超期已完成未变更</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>试验室;总体室</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>跨专业接口澄清耗时</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>测控链路系统接口收敛偏慢</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>影响后续任务7天</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>测控链路系统关键件交付</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>测控主机样机</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>重大节点</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>正常待完成</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>试验室;总体室</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>测控链路系统关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>测控链路系统联调准备</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2027-03-07</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>联调准备报告</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>重要节点</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>超期未完成未变更</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>试验室;总体室</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2027-04-07</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>关键件到货晚于计划</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>测控主机样机交付滞后</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>影响联调窗口排布</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2027-03-17</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>XM-2026-C09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>测控分系统</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>测控链路系统综合联试</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2027-03-21</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2027-04-26</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>综合联试纪要</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>测控室</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>潘总</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>不正常待变更</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>试验室;总体室</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>测控链路系统需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2027-03-21</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>田PM</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2027-05-05</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>田工</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>环境试验保障平台需求基线评审</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>需求基线包</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>柳工</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>试验室</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>曹总</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>按时完成</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>总体室;控制室</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>柳PM</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>环境试验保障平台 需求基线评审一次通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>环境试验保障平台详细设计评审</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>详细设计报告</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>重要节点</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>试验室</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>曹总</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>超期已完成已变更</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>总体室;控制室</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>新增评审意见需要补充闭环</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>环境试验保障平台设计闭环补充验证</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>影响后续任务7天</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>柳PM</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>环境试验保障平台关键件交付</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>综合试验工装</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>重大节点</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>试验室</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>曹总</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>正常待完成</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>全所</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>总体室;控制室</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>质量部</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>环境试验保障平台关键件正按计划推进</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>李所</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>年度计划</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>柳PM</t>
         </is>
       </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>2027-02-08</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>处于窗口期内</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>环境试验保障平台联调准备</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>联调准备报告</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>重要节点</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>试验室</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>曹总</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>超期未完成已变更</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>总体室;控制室</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>质量部</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2027-05-17</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>接口边界调整后重新排产</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>环境试验保障平台联调输入条件变更</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>影响后续综合联试安排</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>柳PM</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2027-04-19</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>XM-2026-C10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>试验分系统</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>环境试验保障平台综合联试</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2027-04-20</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2027-05-26</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>综合联试纪要</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>试验室</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>曹总</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>不正常待变更</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>总体室;控制室</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>科技部</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>发现外部约束变化需发起设计更改</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>环境试验保障平台需新增变更评审</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>影响综合联试基线冻结</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2027-04-20</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>李所</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>年度计划</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>柳PM</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>2027-06-02</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>柳工</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
